--- a/demo/客户生日关怀助手_产品展示数据.xlsx
+++ b/demo/客户生日关怀助手_产品展示数据.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:I49"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -409,6 +409,8 @@
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="30.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -433,6 +435,12 @@
       <c r="G1" t="str">
         <v>备注</v>
       </c>
+      <c r="H1" t="str">
+        <v>所属公司</v>
+      </c>
+      <c r="I1" t="str">
+        <v>职位</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -456,6 +464,12 @@
       <c r="G2" t="str">
         <v>合作5年以上，喜欢茶文化</v>
       </c>
+      <c r="H2" t="str">
+        <v>华兴制造集团</v>
+      </c>
+      <c r="I2" t="str">
+        <v>总经理</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -479,6 +493,12 @@
       <c r="G3" t="str">
         <v>授信续期洽谈中</v>
       </c>
+      <c r="H3" t="str">
+        <v>恒信地产</v>
+      </c>
+      <c r="I3" t="str">
+        <v>董事长</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -502,6 +522,12 @@
       <c r="G4" t="str">
         <v>对公加私行客户</v>
       </c>
+      <c r="H4" t="str">
+        <v>云溪餐饮</v>
+      </c>
+      <c r="I4" t="str">
+        <v>创始人</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -525,6 +551,12 @@
       <c r="G5" t="str">
         <v>关注结算账户</v>
       </c>
+      <c r="H5" t="str">
+        <v>丰汇商贸</v>
+      </c>
+      <c r="I5" t="str">
+        <v>总经理</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -548,6 +580,12 @@
       <c r="G6" t="str">
         <v>合作多年</v>
       </c>
+      <c r="H6" t="str">
+        <v>丰汇商贸</v>
+      </c>
+      <c r="I6" t="str">
+        <v>财务总监</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -571,6 +609,12 @@
       <c r="G7" t="str">
         <v>同业往来</v>
       </c>
+      <c r="H7" t="str">
+        <v>宏远金融</v>
+      </c>
+      <c r="I7" t="str">
+        <v>部门经理</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -594,6 +638,12 @@
       <c r="G8" t="str">
         <v>关注对公结算</v>
       </c>
+      <c r="H8" t="str">
+        <v>中建五局</v>
+      </c>
+      <c r="I8" t="str">
+        <v>项目负责人</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -617,6 +667,12 @@
       <c r="G9" t="str">
         <v>关注理财</v>
       </c>
+      <c r="H9" t="str">
+        <v>蓝海科技</v>
+      </c>
+      <c r="I9" t="str">
+        <v>联合创始人</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -640,6 +696,12 @@
       <c r="G10" t="str">
         <v>小微贷款客户</v>
       </c>
+      <c r="H10" t="str">
+        <v>华兴制造集团</v>
+      </c>
+      <c r="I10" t="str">
+        <v>采购经理</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -663,6 +725,12 @@
       <c r="G11" t="str">
         <v>喜欢茶文化</v>
       </c>
+      <c r="H11" t="str">
+        <v>云溪餐饮</v>
+      </c>
+      <c r="I11" t="str">
+        <v>合伙人</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -686,6 +754,12 @@
       <c r="G12" t="str">
         <v>采购经理</v>
       </c>
+      <c r="H12" t="str">
+        <v>华兴制造集团</v>
+      </c>
+      <c r="I12" t="str">
+        <v>总经理</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -709,6 +783,12 @@
       <c r="G13" t="str">
         <v>企业财务负责人</v>
       </c>
+      <c r="H13" t="str">
+        <v>恒信地产</v>
+      </c>
+      <c r="I13" t="str">
+        <v>财务负责人</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -732,6 +812,12 @@
       <c r="G14" t="str">
         <v>企业负责人</v>
       </c>
+      <c r="H14" t="str">
+        <v>蓝海科技</v>
+      </c>
+      <c r="I14" t="str">
+        <v>CEO</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -755,6 +841,12 @@
       <c r="G15" t="str">
         <v>公益基金会理事</v>
       </c>
+      <c r="H15" t="str">
+        <v>心桥公益基金会</v>
+      </c>
+      <c r="I15" t="str">
+        <v>理事</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -778,6 +870,12 @@
       <c r="G16" t="str">
         <v>同业合作</v>
       </c>
+      <c r="H16" t="str">
+        <v>宏远金融</v>
+      </c>
+      <c r="I16" t="str">
+        <v>高管</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -801,6 +899,12 @@
       <c r="G17" t="str">
         <v>连锁门店负责人</v>
       </c>
+      <c r="H17" t="str">
+        <v>云溪餐饮</v>
+      </c>
+      <c r="I17" t="str">
+        <v>区域负责人</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -824,6 +928,12 @@
       <c r="G18" t="str">
         <v>工程款结算需求</v>
       </c>
+      <c r="H18" t="str">
+        <v>中建五局</v>
+      </c>
+      <c r="I18" t="str">
+        <v>项目负责人</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -847,6 +957,12 @@
       <c r="G19" t="str">
         <v>供应商合作</v>
       </c>
+      <c r="H19" t="str">
+        <v>华兴制造集团</v>
+      </c>
+      <c r="I19" t="str">
+        <v>采购总监</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -870,6 +986,12 @@
       <c r="G20" t="str">
         <v>楼盘按揭合作</v>
       </c>
+      <c r="H20" t="str">
+        <v>恒信地产</v>
+      </c>
+      <c r="I20" t="str">
+        <v>总经理</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -893,6 +1015,12 @@
       <c r="G21" t="str">
         <v>关注跨境支付</v>
       </c>
+      <c r="H21" t="str">
+        <v>蓝海科技</v>
+      </c>
+      <c r="I21" t="str">
+        <v>创始人</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -916,6 +1044,12 @@
       <c r="G22" t="str">
         <v>商会副会长</v>
       </c>
+      <c r="H22" t="str">
+        <v>丰汇商贸</v>
+      </c>
+      <c r="I22" t="str">
+        <v>商会副会长</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -939,6 +1073,12 @@
       <c r="G23" t="str">
         <v>私人银行客户</v>
       </c>
+      <c r="H23" t="str">
+        <v>宏远金融</v>
+      </c>
+      <c r="I23" t="str">
+        <v>私行客户</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -962,6 +1102,12 @@
       <c r="G24" t="str">
         <v>自由职业</v>
       </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -985,6 +1131,12 @@
       <c r="G25" t="str">
         <v>餐饮品牌合伙人</v>
       </c>
+      <c r="H25" t="str">
+        <v>云溪餐饮</v>
+      </c>
+      <c r="I25" t="str">
+        <v>合伙人</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1008,6 +1160,12 @@
       <c r="G26" t="str">
         <v>集团财务总监</v>
       </c>
+      <c r="H26" t="str">
+        <v>华兴制造集团</v>
+      </c>
+      <c r="I26" t="str">
+        <v>财务总监</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1031,6 +1189,12 @@
       <c r="G27" t="str">
         <v>初创企业联合创始人</v>
       </c>
+      <c r="H27" t="str">
+        <v>蓝海科技</v>
+      </c>
+      <c r="I27" t="str">
+        <v>联合创始人</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1054,6 +1218,12 @@
       <c r="G28" t="str">
         <v>施工队负责人</v>
       </c>
+      <c r="H28" t="str">
+        <v>中建五局</v>
+      </c>
+      <c r="I28" t="str">
+        <v>负责人</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1077,6 +1247,12 @@
       <c r="G29" t="str">
         <v>区域总代理</v>
       </c>
+      <c r="H29" t="str">
+        <v>丰汇商贸</v>
+      </c>
+      <c r="I29" t="str">
+        <v>总经理</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1100,6 +1276,12 @@
       <c r="G30" t="str">
         <v>写字楼业主</v>
       </c>
+      <c r="H30" t="str">
+        <v>恒信地产</v>
+      </c>
+      <c r="I30" t="str">
+        <v>业主</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1123,6 +1305,12 @@
       <c r="G31" t="str">
         <v>自媒体创业者</v>
       </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1146,6 +1334,12 @@
       <c r="G32" t="str">
         <v>融资租赁公司高管</v>
       </c>
+      <c r="H32" t="str">
+        <v>宏远金融</v>
+      </c>
+      <c r="I32" t="str">
+        <v>高管</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1169,6 +1363,12 @@
       <c r="G33" t="str">
         <v>月子中心负责人</v>
       </c>
+      <c r="H33" t="str">
+        <v>云溪餐饮</v>
+      </c>
+      <c r="I33" t="str">
+        <v>负责人</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1192,6 +1392,12 @@
       <c r="G34" t="str">
         <v>外贸工厂主</v>
       </c>
+      <c r="H34" t="str">
+        <v>华兴制造集团</v>
+      </c>
+      <c r="I34" t="str">
+        <v>工厂主</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1215,6 +1421,12 @@
       <c r="G35" t="str">
         <v>上市公司董秘</v>
       </c>
+      <c r="H35" t="str">
+        <v>蓝海科技</v>
+      </c>
+      <c r="I35" t="str">
+        <v>董秘</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1238,6 +1450,12 @@
       <c r="G36" t="str">
         <v>老客户，家族企业</v>
       </c>
+      <c r="H36" t="str">
+        <v>中建五局</v>
+      </c>
+      <c r="I36" t="str">
+        <v>董事长</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1261,6 +1479,12 @@
       <c r="G37" t="str">
         <v>保险经纪人</v>
       </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1284,6 +1508,12 @@
       <c r="G38" t="str">
         <v>连锁超市老板</v>
       </c>
+      <c r="H38" t="str">
+        <v>丰汇商贸</v>
+      </c>
+      <c r="I38" t="str">
+        <v>老板</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1307,6 +1537,12 @@
       <c r="G39" t="str">
         <v>支行同业骨干</v>
       </c>
+      <c r="H39" t="str">
+        <v>宏远金融</v>
+      </c>
+      <c r="I39" t="str">
+        <v>骨干</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1330,6 +1566,12 @@
       <c r="G40" t="str">
         <v>精密零件供应商</v>
       </c>
+      <c r="H40" t="str">
+        <v>华兴制造集团</v>
+      </c>
+      <c r="I40" t="str">
+        <v>总经理</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1353,6 +1595,12 @@
       <c r="G41" t="str">
         <v>物业公司总经理</v>
       </c>
+      <c r="H41" t="str">
+        <v>恒信地产</v>
+      </c>
+      <c r="I41" t="str">
+        <v>总经理</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1376,6 +1624,12 @@
       <c r="G42" t="str">
         <v>科技园入驻企业主</v>
       </c>
+      <c r="H42" t="str">
+        <v>蓝海科技</v>
+      </c>
+      <c r="I42" t="str">
+        <v>企业主</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1399,6 +1653,12 @@
       <c r="G43" t="str">
         <v>民宿主理人</v>
       </c>
+      <c r="H43" t="str">
+        <v>云溪餐饮</v>
+      </c>
+      <c r="I43" t="str">
+        <v>主理人</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1422,6 +1682,12 @@
       <c r="G44" t="str">
         <v>收藏爱好者</v>
       </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -1445,6 +1711,12 @@
       <c r="G45" t="str">
         <v>电商代运营</v>
       </c>
+      <c r="H45" t="str">
+        <v>丰汇商贸</v>
+      </c>
+      <c r="I45" t="str">
+        <v>负责人</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1468,6 +1740,12 @@
       <c r="G46" t="str">
         <v>基金公司渠道</v>
       </c>
+      <c r="H46" t="str">
+        <v>宏远金融</v>
+      </c>
+      <c r="I46" t="str">
+        <v>渠道经理</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1491,6 +1769,12 @@
       <c r="G47" t="str">
         <v>项目经理</v>
       </c>
+      <c r="H47" t="str">
+        <v>中建五局</v>
+      </c>
+      <c r="I47" t="str">
+        <v>项目经理</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1514,6 +1798,12 @@
       <c r="G48" t="str">
         <v>港澳客户，委托亲属对接</v>
       </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -1537,17 +1827,23 @@
       <c r="G49" t="str">
         <v>Excel 日期序列号示例（1992-04-10）</v>
       </c>
+      <c r="H49" t="str">
+        <v>蓝海科技</v>
+      </c>
+      <c r="I49" t="str">
+        <v>总经理</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I49"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <cols>
     <col min="1" max="1" width="70.83203125" customWidth="1"/>
   </cols>
@@ -1624,22 +1920,27 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">  · 性别含“未知”示例，生日含“仅月日”示例。</v>
+        <v xml:space="preserve">  · 性别含“未知”示例，生日含“仅月日”示例；</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v xml:space="preserve">  · “所属公司 / 职位”为选填字段，可用于公私联动与客户画像。</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>提示：导入后可在“设置 → 撤销上次导入”一键回退演示数据。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/demo/客户生日关怀助手_产品展示数据.xlsx
+++ b/demo/客户生日关怀助手_产品展示数据.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:J49"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -411,6 +411,7 @@
     <col min="7" max="7" width="30.83203125" customWidth="1"/>
     <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,6 +442,9 @@
       <c r="I1" t="str">
         <v>职位</v>
       </c>
+      <c r="J1" t="str">
+        <v>星标</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -470,6 +474,9 @@
       <c r="I2" t="str">
         <v>总经理</v>
       </c>
+      <c r="J2" t="str">
+        <v>是</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -499,6 +506,9 @@
       <c r="I3" t="str">
         <v>董事长</v>
       </c>
+      <c r="J3" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -528,6 +538,9 @@
       <c r="I4" t="str">
         <v>创始人</v>
       </c>
+      <c r="J4" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -557,6 +570,9 @@
       <c r="I5" t="str">
         <v>总经理</v>
       </c>
+      <c r="J5" t="str">
+        <v>是</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -586,6 +602,9 @@
       <c r="I6" t="str">
         <v>财务总监</v>
       </c>
+      <c r="J6" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -615,6 +634,9 @@
       <c r="I7" t="str">
         <v>部门经理</v>
       </c>
+      <c r="J7" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -644,6 +666,9 @@
       <c r="I8" t="str">
         <v>项目负责人</v>
       </c>
+      <c r="J8" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -673,6 +698,9 @@
       <c r="I9" t="str">
         <v>联合创始人</v>
       </c>
+      <c r="J9" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -702,6 +730,9 @@
       <c r="I10" t="str">
         <v>采购经理</v>
       </c>
+      <c r="J10" t="str">
+        <v>是</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -731,6 +762,9 @@
       <c r="I11" t="str">
         <v>合伙人</v>
       </c>
+      <c r="J11" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -760,6 +794,9 @@
       <c r="I12" t="str">
         <v>总经理</v>
       </c>
+      <c r="J12" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -789,6 +826,9 @@
       <c r="I13" t="str">
         <v>财务负责人</v>
       </c>
+      <c r="J13" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -818,6 +858,9 @@
       <c r="I14" t="str">
         <v>CEO</v>
       </c>
+      <c r="J14" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -847,6 +890,9 @@
       <c r="I15" t="str">
         <v>理事</v>
       </c>
+      <c r="J15" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -876,6 +922,9 @@
       <c r="I16" t="str">
         <v>高管</v>
       </c>
+      <c r="J16" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -905,6 +954,9 @@
       <c r="I17" t="str">
         <v>区域负责人</v>
       </c>
+      <c r="J17" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -934,6 +986,9 @@
       <c r="I18" t="str">
         <v>项目负责人</v>
       </c>
+      <c r="J18" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -963,6 +1018,9 @@
       <c r="I19" t="str">
         <v>采购总监</v>
       </c>
+      <c r="J19" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -992,6 +1050,9 @@
       <c r="I20" t="str">
         <v>总经理</v>
       </c>
+      <c r="J20" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1021,6 +1082,9 @@
       <c r="I21" t="str">
         <v>创始人</v>
       </c>
+      <c r="J21" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1050,6 +1114,9 @@
       <c r="I22" t="str">
         <v>商会副会长</v>
       </c>
+      <c r="J22" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1079,6 +1146,9 @@
       <c r="I23" t="str">
         <v>私行客户</v>
       </c>
+      <c r="J23" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1108,6 +1178,9 @@
       <c r="I24" t="str">
         <v/>
       </c>
+      <c r="J24" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1137,6 +1210,9 @@
       <c r="I25" t="str">
         <v>合伙人</v>
       </c>
+      <c r="J25" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1166,6 +1242,9 @@
       <c r="I26" t="str">
         <v>财务总监</v>
       </c>
+      <c r="J26" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1195,6 +1274,9 @@
       <c r="I27" t="str">
         <v>联合创始人</v>
       </c>
+      <c r="J27" t="str">
+        <v>是</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1224,6 +1306,9 @@
       <c r="I28" t="str">
         <v>负责人</v>
       </c>
+      <c r="J28" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1253,6 +1338,9 @@
       <c r="I29" t="str">
         <v>总经理</v>
       </c>
+      <c r="J29" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1282,6 +1370,9 @@
       <c r="I30" t="str">
         <v>业主</v>
       </c>
+      <c r="J30" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1311,6 +1402,9 @@
       <c r="I31" t="str">
         <v/>
       </c>
+      <c r="J31" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1340,6 +1434,9 @@
       <c r="I32" t="str">
         <v>高管</v>
       </c>
+      <c r="J32" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1369,6 +1466,9 @@
       <c r="I33" t="str">
         <v>负责人</v>
       </c>
+      <c r="J33" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1398,6 +1498,9 @@
       <c r="I34" t="str">
         <v>工厂主</v>
       </c>
+      <c r="J34" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1427,6 +1530,9 @@
       <c r="I35" t="str">
         <v>董秘</v>
       </c>
+      <c r="J35" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1456,6 +1562,9 @@
       <c r="I36" t="str">
         <v>董事长</v>
       </c>
+      <c r="J36" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1485,6 +1594,9 @@
       <c r="I37" t="str">
         <v/>
       </c>
+      <c r="J37" t="str">
+        <v>是</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1514,6 +1626,9 @@
       <c r="I38" t="str">
         <v>老板</v>
       </c>
+      <c r="J38" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1543,6 +1658,9 @@
       <c r="I39" t="str">
         <v>骨干</v>
       </c>
+      <c r="J39" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1572,6 +1690,9 @@
       <c r="I40" t="str">
         <v>总经理</v>
       </c>
+      <c r="J40" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1601,6 +1722,9 @@
       <c r="I41" t="str">
         <v>总经理</v>
       </c>
+      <c r="J41" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1630,6 +1754,9 @@
       <c r="I42" t="str">
         <v>企业主</v>
       </c>
+      <c r="J42" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1659,6 +1786,9 @@
       <c r="I43" t="str">
         <v>主理人</v>
       </c>
+      <c r="J43" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1688,6 +1818,9 @@
       <c r="I44" t="str">
         <v/>
       </c>
+      <c r="J44" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -1717,6 +1850,9 @@
       <c r="I45" t="str">
         <v>负责人</v>
       </c>
+      <c r="J45" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1746,6 +1882,9 @@
       <c r="I46" t="str">
         <v>渠道经理</v>
       </c>
+      <c r="J46" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1775,6 +1914,9 @@
       <c r="I47" t="str">
         <v>项目经理</v>
       </c>
+      <c r="J47" t="str">
+        <v>否</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1804,6 +1946,9 @@
       <c r="I48" t="str">
         <v/>
       </c>
+      <c r="J48" t="str">
+        <v>是</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -1833,17 +1978,20 @@
       <c r="I49" t="str">
         <v>总经理</v>
       </c>
+      <c r="J49" t="str">
+        <v>否</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J49"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A20"/>
   <cols>
     <col min="1" max="1" width="70.83203125" customWidth="1"/>
   </cols>
@@ -1930,17 +2078,27 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v xml:space="preserve">  · “星标”列可标记重点客户（不受等级限制，如 C 类黄先生、魏女士）；</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v xml:space="preserve">  · 录入完整年份的客户，系统自动展示年龄、属相、本命年、星座标签。</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>提示：导入后可在“设置 → 撤销上次导入”一键回退演示数据。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A20"/>
   </ignoredErrors>
 </worksheet>
 </file>